--- a/02.FOMD/04.metadata_effectsize/fomd_fun/comparison_practice.xlsx
+++ b/02.FOMD/04.metadata_effectsize/fomd_fun/comparison_practice.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/04.metadata_effectsize/fomd_fun/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="8_{4A704683-73A2-468D-ACFE-81CAD09C0DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{301D90CA-AA90-4BF8-8DB8-FC34ED78A68B}"/>
+  <xr:revisionPtr revIDLastSave="408" documentId="8_{4A704683-73A2-468D-ACFE-81CAD09C0DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D2C70C1-6FAE-4EDE-8E26-B1C93B4A3F4D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="870" windowWidth="29040" windowHeight="15720" xr2:uid="{B5D80FD3-C098-4ACC-A509-E5C3699EB74E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{B5D80FD3-C098-4ACC-A509-E5C3699EB74E}"/>
   </bookViews>
   <sheets>
     <sheet name="CT_practice" sheetId="3" r:id="rId1"/>
-    <sheet name="CT_practicetheme" sheetId="1" r:id="rId2"/>
+    <sheet name="CT_subpractice" sheetId="4" r:id="rId2"/>
+    <sheet name="CT_practicetheme" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CT_practice!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CT_subpractice!$A$1:$D$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="159">
   <si>
     <t>no</t>
   </si>
@@ -238,13 +240,295 @@
   </si>
   <si>
     <t>C: No Fertilizers Applied_vs_T: Inorganic Fertilizer..Organic Fertilizer</t>
+  </si>
+  <si>
+    <t>CT_subpractice_col</t>
+  </si>
+  <si>
+    <t>CT_subpractice</t>
+  </si>
+  <si>
+    <t>CT_subpractice_rename</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Herbicide</t>
+  </si>
+  <si>
+    <t>CT_chem_subpractice</t>
+  </si>
+  <si>
+    <t>C: No Herbicide Applied_vs_T: Herbicide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Herbicide..Herbicide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Herbicide..Herbicide..Herbicide</t>
+  </si>
+  <si>
+    <t>n_rows</t>
+  </si>
+  <si>
+    <t>C: Herbicide..Fungicide..Insecticide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Herbicide..Fungicide..Insecticide_vs_T: No Herbicide Applied..No Fungicide Applied..No Insecticide Applied</t>
+  </si>
+  <si>
+    <t>C: Biofungicide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Biofungicide_vs_T: No Fungicide Applied</t>
+  </si>
+  <si>
+    <t>C: Insecticide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Seed inoculation</t>
+  </si>
+  <si>
+    <t>C: No Inoculation Applied_vs_T: Seed inoculation</t>
+  </si>
+  <si>
+    <t>C: Herbicide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Biopesticide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Animal (Vaccine)..Animal (Antibiotic)..Animal (Growth Promoter)_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Antistress_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Biofertilizer..Biofertilizer_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Biofertilizer_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Fungicide..Insecticide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Fungicide..Insecticide_vs_T: No Fungicide Applied..No Insecticide Applied</t>
+  </si>
+  <si>
+    <t>C: Fungicide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Herbicide..Herbicide..Herbicide..Herbicide..Fungicide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Herbicide..Herbicide..Herbicide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Herbicide..Herbicide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Herbicide..Herbicide_vs_T: No Herbicide Applied..No Herbicide Applied</t>
+  </si>
+  <si>
+    <t>C: Herbicide..Herbicide..Herbicide_vs_T: No Herbicide Applied..No Herbicide Applied..No Herbicide Applied</t>
+  </si>
+  <si>
+    <t>C: Herbicide..Herbicide..Herbicide..Herbicide..Fungicide_vs_T: No Herbicide Applied..No Herbicide Applied..No Herbicide Applied..No Herbicide Applied..No Fungicide Applied</t>
+  </si>
+  <si>
+    <t>C: Fungicide_vs_T: No Fungicide Applied</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Animal (Antiparasitic)..Animal (Acaricide)..Animal (Vaccine)</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Animal (Vaccine)..Animal (Antibiotic)..Animal (Growth Promoter)</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Antistress</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Biofertilizer</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Biofertilizer..Biofertilizer</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Biofertilizer..Biofertilizer..Biofertilizer</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Biofertilizer..Biofertilizer..Biofertilizer..Soil inoculation</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Biofungicide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Biopesticide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Fungicide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Fungicide..Fungicide..Fungicide..Fungicide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Herbicide..Fungicide..Insecticide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Herbicide..Herbicide..Herbicide..Herbicide..Herbicide..Herbicide..Herbicide..Herbicide..Herbicide..Herbicide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Insecticide</t>
+  </si>
+  <si>
+    <t>C: No Fungicide Applied_vs_T: Fungicide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Insecticide..Insecticide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Other</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Other..Other</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Other..Seed inoculation</t>
+  </si>
+  <si>
+    <t>C: No Fungicide Applied_vs_T: Biofungicide</t>
+  </si>
+  <si>
+    <t>C: No Fungicide Applied..No Fungicide Applied..No Fungicide Applied..No Fungicide Applied_vs_T: Fungicide..Fungicide..Fungicide..Fungicide</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Seed inoculation..Seed inoculation..Seed inoculation</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Soil inoculation</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Soil inoculation..Soil inoculation</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application_vs_T: Unspecified (if pesticide org or inorg was applied)..Seed inoculation..Seed inoculation</t>
+  </si>
+  <si>
+    <t>C: Other..Other_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Seed inoculation..Other_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Seed inoculation..Seed inoculation..Seed inoculation_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Seed inoculation_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: Antistress_vs_T: No Antistress Applied</t>
+  </si>
+  <si>
+    <t>C: No Antistress Applied_vs_T: Antistress</t>
+  </si>
+  <si>
+    <t>C: No Biofertilizer Applied_vs_T: Biofertilizer</t>
+  </si>
+  <si>
+    <t>C: Animal (Vaccine)..Animal (Antibiotic)..Animal (Growth Promoter)_vs_T: No Vaccine Applied..No Antibiotic Applied..No Growth Promoter Applied</t>
+  </si>
+  <si>
+    <t>C: No Vaccine Applied..No Antibiotic Applied..No Growth Promoter Applied_vs_T: Animal (Vaccine)..Animal (Antibiotic)..Animal (Growth Promoter)</t>
+  </si>
+  <si>
+    <t>C: No Herbicide Applied..No Herbicide Applied..No Herbicide Applied..No Herbicide Applied..No Herbicide Applied..No Herbicide Applied..No Herbicide Applied..No Herbicide Applied..No Herbicide Applied..No Herbicide Applied_vs_T: Herbicide..Herbicide..Herbicide..Herbicide..Herbicide..Herbicide..Herbicide..Herbicide..Herbicide..Herbicide</t>
+  </si>
+  <si>
+    <t>C: Biofertilizer..Biofertilizer_vs_T: No Biofertilizer Applied</t>
+  </si>
+  <si>
+    <t>C: Biofertilizer..Biofertilizer_vs_T: No Biofertilizer Applied..No Biofertilizer Applied</t>
+  </si>
+  <si>
+    <t>C: No Biofertilizer Applied..No Biofertilizer Applied_vs_T: Biofertilizer</t>
+  </si>
+  <si>
+    <t>C: No Biofertilizer Applied..No Biofertilizer Applied..No Biofertilizer Applied_vs_T: Biofertilizer</t>
+  </si>
+  <si>
+    <t>C: No Biofertilizer Applied..No Biofertilizer Applied..No Biofertilizer Applied..No Inoculation Applied_vs_T: Biofertilizer..Biofertilizer..Biofertilizer..Soil inoculation</t>
+  </si>
+  <si>
+    <t>C: No Antiparasitic Applied..No Acaricide Applied..No Vaccine Applied_vs_T: Animal (Antiparasitic)..Animal (Acaricide)..Animal (Vaccine)</t>
+  </si>
+  <si>
+    <t>C: No Inoculation Applied_vs_T: Seed inoculation..Seed inoculation</t>
+  </si>
+  <si>
+    <t>C: No Inoculation Applied..No Inoculation Applied_vs_T: Soil inoculation..Soil inoculation</t>
+  </si>
+  <si>
+    <t>C: Seed inoculation..Seed inoculation..Seed inoculation_vs_T: No Chemical Application..No Inoculation Applied..No Inoculation Applied</t>
+  </si>
+  <si>
+    <t>C: Seed inoculation_vs_T: No Inoculation Applied</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application..No Inoculation Applied..No Inoculation Applied_vs_T: Seed inoculation..Seed inoculation..Seed inoculation</t>
+  </si>
+  <si>
+    <t>C: No Inoculation Applied_vs_T: Soil inoculation</t>
+  </si>
+  <si>
+    <t>C: Herbicide_vs_T: No Herbicide Applied</t>
+  </si>
+  <si>
+    <t>C: No Pesticides Applied_vs_T: Biopesticide</t>
+  </si>
+  <si>
+    <t>C: Biopesticide_vs_T: No Pesticides Applied</t>
+  </si>
+  <si>
+    <t>C: No Insecticide Applied_vs_T: Insecticide</t>
+  </si>
+  <si>
+    <t>C: Insecticide_vs_T: No Insecticide Applied</t>
+  </si>
+  <si>
+    <t>C: No Insecticide Applied..No Insecticide Applied_vs_T: Insecticide..Insecticide</t>
+  </si>
+  <si>
+    <t>C: No Herbicide Applied..No Fungicide Applied..No Insecticide Applied_vs_T: Herbicide..Fungicide..Insecticide</t>
+  </si>
+  <si>
+    <t>C: Insecticide..Insecticide_vs_T: No Chemical Application</t>
+  </si>
+  <si>
+    <t>C: No Chemical Application..No Inoculation Applied..No Inoculation Applied_vs_T: Seed inoculation..Seed inoculation..Seed inoculation</t>
+  </si>
+  <si>
+    <t>C: Seed inoculation..Seed inoculation..Seed inoculation_vs_T: No Chemical Application..No Inoculation Applied..No Inoculation Applied</t>
+  </si>
+  <si>
+    <t>C: No Inoculation Applied..No Inoculation Applied..No Inoculation Applied_vs_T: Seed inoculation..Seed inoculation..Seed inoculation</t>
+  </si>
+  <si>
+    <t>C: Insecticide..Insecticide_vs_T: No Insecticide Applied..No Insecticide Applied</t>
+  </si>
+  <si>
+    <t>C: Seed inoculation..Seed inoculation..Seed inoculation_vs_T: No Inoculation Applied..No Inoculation Applied..No Inoculation Applied</t>
+  </si>
+  <si>
+    <t>C: NA...Manual_vs_T: Herbicide..Herbicide..Herbicide</t>
+  </si>
+  <si>
+    <t>C: Manual_vs_T: Herbicide..Herbicide..Herbicide</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,8 +544,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,8 +564,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -283,19 +579,475 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFD6DADC"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD6DADC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="44">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -625,16 +1377,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1BB83AA-B54B-4B5B-AF1A-3A125FCD1788}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="49.42578125" customWidth="1"/>
-    <col min="2" max="2" width="78.5703125" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" customWidth="1"/>
+    <col min="1" max="1" width="49.453125" customWidth="1"/>
+    <col min="2" max="2" width="78.54296875" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>54</v>
       </c>
@@ -648,7 +1400,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -659,7 +1411,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -670,7 +1422,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -681,7 +1433,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -692,7 +1444,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -703,7 +1455,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -714,7 +1466,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -725,7 +1477,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -736,7 +1488,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -747,7 +1499,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -758,7 +1510,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -769,7 +1521,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -780,7 +1532,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -791,7 +1543,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -802,7 +1554,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -813,7 +1565,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -824,7 +1576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -835,7 +1587,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -846,7 +1598,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -857,30 +1609,664 @@
         <v>63</v>
       </c>
     </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D19" xr:uid="{F1BB83AA-B54B-4B5B-AF1A-3A125FCD1788}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D19">
-      <sortCondition ref="C2:C19"/>
-      <sortCondition ref="A2:A19"/>
-      <sortCondition ref="B2:B19"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:D19" xr:uid="{F1BB83AA-B54B-4B5B-AF1A-3A125FCD1788}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF149DD-3563-4A6A-B8D7-B80D17C24E72}">
+  <dimension ref="A1:D49"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.7265625" customWidth="1"/>
+    <col min="2" max="2" width="113.81640625" customWidth="1"/>
+    <col min="3" max="3" width="36.36328125" customWidth="1"/>
+    <col min="4" max="6" width="28.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D48" xr:uid="{1AF149DD-3563-4A6A-B8D7-B80D17C24E72}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D37">
+    <sortCondition ref="B2:B37"/>
+  </sortState>
+  <conditionalFormatting sqref="B1:B37 B48 B50:B1048576">
+    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B37">
+    <cfRule type="duplicateValues" dxfId="42" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B45">
+    <cfRule type="duplicateValues" dxfId="41" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48:C48">
+    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2">
+    <cfRule type="duplicateValues" dxfId="38" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3">
+    <cfRule type="duplicateValues" dxfId="35" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C5">
+    <cfRule type="duplicateValues" dxfId="32" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17">
+    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18">
+    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:C21">
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22">
+    <cfRule type="duplicateValues" dxfId="17" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23">
+    <cfRule type="duplicateValues" dxfId="14" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24">
+    <cfRule type="duplicateValues" dxfId="12" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C28">
+    <cfRule type="duplicateValues" dxfId="10" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29">
+    <cfRule type="duplicateValues" dxfId="8" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C31">
+    <cfRule type="duplicateValues" dxfId="6" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C33">
+    <cfRule type="duplicateValues" dxfId="3" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C41">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C48">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314A9E21-D9D2-4511-96A5-F37E76693898}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="85.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" customWidth="1"/>
+    <col min="2" max="2" width="85.7265625" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -891,7 +2277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -902,7 +2288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -913,7 +2299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -924,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -935,7 +2321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -946,7 +2332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -957,7 +2343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -968,7 +2354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -979,7 +2365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -990,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1001,7 +2387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1009,7 +2395,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1017,7 +2403,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1025,7 +2411,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1033,7 +2419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1041,7 +2427,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1049,7 +2435,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1063,26 +2449,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -1283,26 +2649,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{107F0679-E8DE-4195-A337-2B53D0BEA873}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C13F900-E3DA-4B9A-97E9-47FD2205EAE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{131AC24A-5D72-4127-A006-E64EAB7D3A44}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1319,4 +2686,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C13F900-E3DA-4B9A-97E9-47FD2205EAE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{107F0679-E8DE-4195-A337-2B53D0BEA873}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02.FOMD/04.metadata_effectsize/fomd_fun/comparison_practice.xlsx
+++ b/02.FOMD/04.metadata_effectsize/fomd_fun/comparison_practice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/04.metadata_effectsize/fomd_fun/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="408" documentId="8_{4A704683-73A2-468D-ACFE-81CAD09C0DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D2C70C1-6FAE-4EDE-8E26-B1C93B4A3F4D}"/>
+  <xr:revisionPtr revIDLastSave="414" documentId="8_{4A704683-73A2-468D-ACFE-81CAD09C0DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA8BA543-D653-47D6-9EB7-0D6DC95D2ADD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{B5D80FD3-C098-4ACC-A509-E5C3699EB74E}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="1" xr2:uid="{B5D80FD3-C098-4ACC-A509-E5C3699EB74E}"/>
   </bookViews>
   <sheets>
     <sheet name="CT_practice" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CT_practice!$A$1:$D$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CT_subpractice!$A$1:$D$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CT_subpractice!$A$1:$D$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="161">
   <si>
     <t>no</t>
   </si>
@@ -522,6 +522,12 @@
   </si>
   <si>
     <t>C: Manual_vs_T: Herbicide..Herbicide..Herbicide</t>
+  </si>
+  <si>
+    <t>"C: No Chemical Application_vs_T: Animal (Vaccine)..Animal (Antibiotic)..Growth Promoter"</t>
+  </si>
+  <si>
+    <t>"C: No Vaccine Applied..No Antibiotic Applied..No Growth Promoter Applied_vs_T: Animal (Vaccine)..Animal (Antibiotic)..Growth Promoter"</t>
   </si>
 </sst>
 </file>
@@ -606,7 +612,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="45">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1622,7 +1638,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF149DD-3563-4A6A-B8D7-B80D17C24E72}">
-  <dimension ref="A1:D49"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.7265625" customWidth="1"/>
@@ -1656,7 +1673,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -1667,7 +1684,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -1678,7 +1695,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>69</v>
       </c>
@@ -1689,7 +1706,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>69</v>
       </c>
@@ -1700,7 +1717,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>69</v>
       </c>
@@ -1711,7 +1728,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>69</v>
       </c>
@@ -1722,7 +1739,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -1733,7 +1750,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -1744,7 +1761,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -1755,7 +1772,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>69</v>
       </c>
@@ -1766,7 +1783,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>69</v>
       </c>
@@ -1777,7 +1794,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -1788,7 +1805,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -1821,7 +1838,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -1832,7 +1849,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -1843,7 +1860,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -1854,7 +1871,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>69</v>
       </c>
@@ -1865,7 +1882,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>69</v>
       </c>
@@ -1876,7 +1893,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -1887,7 +1904,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -1898,7 +1915,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>69</v>
       </c>
@@ -1909,7 +1926,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -1920,7 +1937,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -1931,7 +1948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -1942,7 +1959,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1953,7 +1970,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1964,7 +1981,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>69</v>
       </c>
@@ -1975,7 +1992,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>69</v>
       </c>
@@ -1986,7 +2003,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1997,7 +2014,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -2006,7 +2023,7 @@
       </c>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -2015,7 +2032,7 @@
       </c>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -2024,7 +2041,7 @@
       </c>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>69</v>
       </c>
@@ -2035,7 +2052,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>69</v>
       </c>
@@ -2046,7 +2063,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>69</v>
       </c>
@@ -2057,7 +2074,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -2068,7 +2085,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -2079,7 +2096,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>69</v>
       </c>
@@ -2088,7 +2105,7 @@
       </c>
       <c r="C42" s="3"/>
     </row>
-    <row r="43" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>69</v>
       </c>
@@ -2097,7 +2114,7 @@
       </c>
       <c r="C43" s="3"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>69</v>
       </c>
@@ -2108,7 +2125,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>69</v>
       </c>
@@ -2119,7 +2136,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>69</v>
       </c>
@@ -2130,7 +2147,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>69</v>
       </c>
@@ -2141,7 +2158,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>69</v>
       </c>
@@ -2152,7 +2169,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>69</v>
       </c>
@@ -2163,93 +2180,116 @@
         <v>158</v>
       </c>
     </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" t="s">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D48" xr:uid="{1AF149DD-3563-4A6A-B8D7-B80D17C24E72}"/>
+  <autoFilter ref="A1:D50" xr:uid="{1AF149DD-3563-4A6A-B8D7-B80D17C24E72}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="&quot;C: No Chemical Application_vs_T: Animal (Vaccine)..Animal (Antibiotic)..Growth Promoter&quot;"/>
+        <filter val="C: Animal (Vaccine)..Animal (Antibiotic)..Animal (Growth Promoter)_vs_T: No Chemical Application"/>
+        <filter val="C: No Chemical Application_vs_T: Animal (Antiparasitic)..Animal (Acaricide)..Animal (Vaccine)"/>
+        <filter val="C: No Chemical Application_vs_T: Animal (Vaccine)..Animal (Antibiotic)..Animal (Growth Promoter)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D37">
     <sortCondition ref="B2:B37"/>
   </sortState>
-  <conditionalFormatting sqref="B1:B37 B48 B50:B1048576">
-    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
+  <conditionalFormatting sqref="B1:B37 B48 B51:B1048576">
+    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B37">
-    <cfRule type="duplicateValues" dxfId="42" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B45">
-    <cfRule type="duplicateValues" dxfId="41" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:C48">
-    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="duplicateValues" dxfId="38" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
+    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
     <cfRule type="duplicateValues" dxfId="35" priority="31"/>
     <cfRule type="duplicateValues" dxfId="34" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C5">
-    <cfRule type="duplicateValues" dxfId="32" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19:C21">
-    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
     <cfRule type="duplicateValues" dxfId="19" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22">
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
     <cfRule type="duplicateValues" dxfId="17" priority="10"/>
     <cfRule type="duplicateValues" dxfId="16" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23">
-    <cfRule type="duplicateValues" dxfId="14" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24">
-    <cfRule type="duplicateValues" dxfId="12" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28">
-    <cfRule type="duplicateValues" dxfId="10" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29">
-    <cfRule type="duplicateValues" dxfId="8" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C31">
-    <cfRule type="duplicateValues" dxfId="6" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33">
-    <cfRule type="duplicateValues" dxfId="3" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C41">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C48">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50:C50">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2449,6 +2489,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -2649,27 +2709,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{107F0679-E8DE-4195-A337-2B53D0BEA873}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C13F900-E3DA-4B9A-97E9-47FD2205EAE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{131AC24A-5D72-4127-A006-E64EAB7D3A44}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2686,23 +2745,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C13F900-E3DA-4B9A-97E9-47FD2205EAE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{107F0679-E8DE-4195-A337-2B53D0BEA873}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>